--- a/survey_templates/037_online_professional_skills_course_poll--survey_templates.xlsx
+++ b/survey_templates/037_online_professional_skills_course_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1625,17 +1625,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>communication_skills_choices</t>
+          <t>delivery_format_survey_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Communication skills</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>blended</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Blended</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>blended</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blended</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -1698,29 +1698,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>delivery_format_survey_choices</t>
+          <t>online_delivery_format_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>video-based</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Video-based</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>video-based</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Video-based</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1766,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>online_delivery_format_choices</t>
+          <t>online_delivery_features_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Live chat</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>live_chat</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Live chat</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>gamification</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Gamification</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gamification</t>
+          <t>gamified</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gamification</t>
+          <t>Gamified</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gamified</t>
+          <t>discussion_forum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gamified</t>
+          <t>Discussion forum</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>discussion_forum</t>
+          <t>interactive_simulations</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Discussion forum</t>
+          <t>Interactive simulations</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>interactive_simulations</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Interactive simulations</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>ai-powered</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>AI-powered</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ai-powered</t>
+          <t>gamified_content</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AI-powered</t>
+          <t>Gamified content</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gamified_content</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gamified content</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>ai-powered_chatbots</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>AI-powered chatbots</t>
         </is>
       </c>
     </row>
@@ -1987,46 +1987,46 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ai-powered_chatbots</t>
+          <t>gamified_assessments</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AI-powered chatbots</t>
+          <t>Gamified assessments</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>online_delivery_features_choices</t>
+          <t>in_person_survey_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gamified_assessments</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gamified assessments</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>online_delivery_features_choices</t>
+          <t>in_person_survey_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
@@ -2055,19 +2055,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>live_training</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Live training</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>in_person_survey_choices</t>
+          <t>on_the_job_survey_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2084,102 +2084,102 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>in_person_survey_choices</t>
+          <t>on_the_job_survey_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>live_training</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Live training</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>in_person_survey_choices</t>
+          <t>self_paced_survey_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>on_the_job_survey_choices</t>
+          <t>self_paced_survey_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>on_the_job_survey_choices</t>
+          <t>blended_survey_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>blended</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Blended</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>self_paced_survey_choices</t>
+          <t>blended_survey_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>self_paced_survey_choices</t>
+          <t>blended_survey_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>live_training</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Live training</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>blended</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Blended</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
@@ -2225,70 +2225,70 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>live_training</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Live training</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>blended_survey_choices</t>
+          <t>online_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>blended_survey_choices</t>
+          <t>online_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>blended_survey_choices</t>
+          <t>online_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>online_presentation_survey_choices</t>
+          <t>online_video_survey_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2305,34 +2305,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>online_presentation_survey_choices</t>
+          <t>online_video_survey_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>online_presentation_survey_choices</t>
+          <t>online_video_survey_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>ai-powered</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>AI-powered</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ai-powered</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI-powered</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -2412,63 +2412,63 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>online_video_survey_choices</t>
+          <t>blended_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>online_video_survey_choices</t>
+          <t>blended_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>online_video_survey_choices</t>
+          <t>blended_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
@@ -2514,80 +2514,80 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>blended_presentation_survey_choices</t>
+          <t>in_person_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>blended_presentation_survey_choices</t>
+          <t>in_person_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>blended_presentation_survey_choices</t>
+          <t>in_person_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>blended_presentation_survey_choices</t>
+          <t>in_person_presentation_survey_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
@@ -2616,80 +2616,80 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>in_person_presentation_survey_choices</t>
+          <t>blended_video_survey_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>in_person_presentation_survey_choices</t>
+          <t>blended_video_survey_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>in_person_presentation_survey_choices</t>
+          <t>blended_video_survey_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>in_person_presentation_survey_choices</t>
+          <t>blended_video_survey_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -2735,36 +2735,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>blended_video_survey_choices</t>
+          <t>online_video_survey_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>blended_video_survey_choices</t>
+          <t>online_video_survey_2_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2781,24 +2781,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>blended_video_survey_choices</t>
+          <t>online_video_survey_2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>ai-powered</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>AI-powered</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>blended_video_survey_choices</t>
+          <t>online_video_survey_2_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ai-powered</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AI-powered</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -2871,80 +2871,80 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>online_video_survey_2_choices</t>
+          <t>presentation_preferences_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>online_video_survey_2_choices</t>
+          <t>presentation_preferences_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>online_video_survey_2_choices</t>
+          <t>presentation_preferences_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>online_video_survey_2_choices</t>
+          <t>presentation_preferences_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -3007,36 +3007,36 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>presentation_preferences_choices</t>
+          <t>presentation_features_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>presentation_preferences_choices</t>
+          <t>presentation_features_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3053,34 +3053,34 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>presentation_preferences_choices</t>
+          <t>presentation_features_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>presentation_preferences_choices</t>
+          <t>presentation_features_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
@@ -3109,97 +3109,97 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>presentation_features_choices</t>
+          <t>presentation_delivery_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>presentation_features_choices</t>
+          <t>presentation_delivery_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>presentation_features_choices</t>
+          <t>presentation_delivery_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>presentation_features_choices</t>
+          <t>presentation_delivery_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>presentation_features_choices</t>
+          <t>presentation_delivery_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>presentation_delivery_choices</t>
+          <t>video_production_survey_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3257,68 +3257,68 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>presentation_delivery_choices</t>
+          <t>video_production_survey_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>presentation_delivery_choices</t>
+          <t>video_production_survey_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>presentation_delivery_choices</t>
+          <t>video_production_survey_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>self-paced_learning</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>Self-paced learning</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>presentation_delivery_choices</t>
+          <t>video_production_survey_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3330,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
@@ -3364,97 +3364,97 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>video_production_survey_choices</t>
+          <t>video_delivery_survey_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>self-paced_learning</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Self-paced learning</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>video_production_survey_choices</t>
+          <t>video_delivery_survey_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>video_production_survey_choices</t>
+          <t>video_delivery_survey_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>video_production_survey_choices</t>
+          <t>video_delivery_survey_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>video_production_survey_choices</t>
+          <t>video_delivery_survey_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -3500,97 +3500,97 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>video_delivery_survey_choices</t>
+          <t>video_survey_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>video_delivery_survey_choices</t>
+          <t>video_survey_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>video_delivery_survey_choices</t>
+          <t>video_survey_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>ai-powered</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>AI-powered</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>video_delivery_survey_choices</t>
+          <t>video_survey_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>video_delivery_survey_choices</t>
+          <t>video_survey_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -3636,97 +3636,97 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ai-powered</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AI-powered</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>video_survey_choices</t>
+          <t>delivery_preferences_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>video_survey_choices</t>
+          <t>delivery_preferences_choices</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>video_survey_choices</t>
+          <t>delivery_preferences_choices</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>face-to-face</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Face-to-face</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>video_survey_choices</t>
+          <t>delivery_preferences_choices</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>video_survey_choices</t>
+          <t>delivery_preferences_choices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>on-the-job_training</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>On-the-job training</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>in-person_training</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>In-person training</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
@@ -3772,97 +3772,97 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>face-to-face</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Face-to-face</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>delivery_preferences_choices</t>
+          <t>video_survey_2_choices</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>interactive</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Interactive</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>delivery_preferences_choices</t>
+          <t>video_survey_2_choices</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>on-the-job_training</t>
+          <t>video_recording</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>On-the-job training</t>
+          <t>Video recording</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>delivery_preferences_choices</t>
+          <t>video_survey_2_choices</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>in-person_training</t>
+          <t>ai-powered_analytics</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>In-person training</t>
+          <t>AI-powered analytics</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>delivery_preferences_choices</t>
+          <t>video_survey_2_choices</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>live-based</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Live-based</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>delivery_preferences_choices</t>
+          <t>video_survey_2_choices</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Self-paced</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>interactive</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Interactive</t>
+          <t>3D modeling</t>
         </is>
       </c>
     </row>
@@ -3891,97 +3891,97 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>video_recording</t>
+          <t>chatbots</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Video recording</t>
+          <t>Chatbots</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>video_survey_2_choices</t>
+          <t>skills_survey_choices</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ai-powered_analytics</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AI-powered analytics</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>video_survey_2_choices</t>
+          <t>skills_survey_choices</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>live-based</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Live-based</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>video_survey_2_choices</t>
+          <t>skills_survey_choices</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>self-paced</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Self-paced</t>
+          <t>Project management</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>video_survey_2_choices</t>
+          <t>skills_survey_choices</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>3D modeling</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>video_survey_2_choices</t>
+          <t>skills_survey_choices</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>chatbots</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>data_visualization</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Data Visualization</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>web_development</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Project management</t>
+          <t>Web Development</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4044,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>ui/ux</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>UI/UX</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>artificial_intelligence</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>data_analysis</t>
+          <t>data_science</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Data Science</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>data_visualization</t>
+          <t>cyber_security</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Data Visualization</t>
+          <t>Cyber Security</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>web_development</t>
+          <t>digital_marketing</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ui/ux</t>
+          <t>business_analysis</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Business Analysis</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>artificial_intelligence</t>
+          <t>cloud_computing</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>data_science</t>
+          <t>machine_learning</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Machine Learning</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cyber_security</t>
+          <t>business_intelligence</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Business Intelligence</t>
         </is>
       </c>
     </row>
@@ -4197,95 +4197,10 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>digital_marketing</t>
+          <t>network_security</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
-        <is>
-          <t>Digital Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>skills_survey_choices</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>business_analysis</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Business Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>skills_survey_choices</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>cloud_computing</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Cloud Computing</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>skills_survey_choices</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>machine_learning</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>skills_survey_choices</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>business_intelligence</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Business Intelligence</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>skills_survey_choices</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>network_security</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
         <is>
           <t>Network Security</t>
         </is>
